--- a/templates/check_android_ai.xlsx
+++ b/templates/check_android_ai.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutoReport_AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutoReport_AI\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8402BDC-4AB4-4773-91B5-F1D530F3B211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB9606C-276E-4585-9785-EBFDC14FDC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29490" yWindow="2340" windowWidth="27135" windowHeight="14850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Android App" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="153">
   <si>
     <t>分類</t>
   </si>
@@ -503,12 +503,900 @@
     <t>score</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試方式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>透過</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CMAS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>進行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>檢測。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試結果：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>無加殼保護</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>無開啟螢幕覆蓋防護功能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>存取敏感數據權限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>皆為必要權限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>無檢查設備安全存取策略</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+5.WebView</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>允許存取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>File (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>僅載入本機資料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>必須在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>root</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>的權限下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>或是環境下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，螢幕覆蓋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>攻擊及敏感數據權限存取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>才有可能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>發生風險</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>既有防護／限制條件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>無</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試方式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>透過</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>app</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>介面輸入特殊字元、特長字串等等，檢視程式是否會發生異常。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試結果：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>app</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>中的輸入欄位有進行基本長度過濾，經測試無發現異常</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試方式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>透過</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>grypr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>進行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sbom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>檢測。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試結果：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>無發現</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>風險，但是會建議廠商持續根據第三方套件的最新版，進行持續更版。</t>
+    </r>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試方式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>透過</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>checkmarx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>工具進行檢測</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試結果：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>無</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>發現高風險。有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>個中風險，但是因為真實使用情境不會發生，故判定可以降低風險，有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>個低風險，但是判斷風險值極低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>上述所判斷的中風險必須在特定的權限或是條件下，才有可能發生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>既有防護／限制條件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>在輸入時利用函式進行輸出入檢查，故可以降風險</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29">
+  <fonts count="34">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -698,6 +1586,40 @@
       <sz val="9"/>
       <name val="細明體"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -918,7 +1840,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1068,6 +1990,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1507,7 +2432,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="25" customHeight="1">
+    <row r="2" spans="1:11" ht="150" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
@@ -1518,9 +2443,11 @@
         <v>8</v>
       </c>
       <c r="D2" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="46"/>
+        <v>19</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>152</v>
+      </c>
       <c r="F2" s="46"/>
       <c r="G2" s="46"/>
       <c r="H2" s="46" t="s">
@@ -1530,7 +2457,7 @@
       <c r="J2" s="46"/>
       <c r="K2" s="46"/>
     </row>
-    <row r="3" spans="1:11" ht="25" customHeight="1">
+    <row r="3" spans="1:11" ht="150" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
@@ -1541,9 +2468,11 @@
         <v>10</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="46"/>
+        <v>20</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>151</v>
+      </c>
       <c r="F3" s="46"/>
       <c r="G3" s="46"/>
       <c r="H3" s="46" t="s">
@@ -1553,7 +2482,7 @@
       <c r="J3" s="46"/>
       <c r="K3" s="46"/>
     </row>
-    <row r="4" spans="1:11" ht="25" customHeight="1">
+    <row r="4" spans="1:11" ht="150" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>11</v>
       </c>
@@ -1564,9 +2493,11 @@
         <v>13</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="46"/>
+        <v>19</v>
+      </c>
+      <c r="E4" s="56" t="s">
+        <v>149</v>
+      </c>
       <c r="F4" s="46"/>
       <c r="G4" s="46"/>
       <c r="H4" s="46" t="s">
@@ -1576,7 +2507,7 @@
       <c r="J4" s="46"/>
       <c r="K4" s="46"/>
     </row>
-    <row r="5" spans="1:11" ht="25" customHeight="1">
+    <row r="5" spans="1:11" ht="150" customHeight="1">
       <c r="A5" s="50" t="s">
         <v>14</v>
       </c>
@@ -1587,9 +2518,11 @@
         <v>142</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="46"/>
+        <v>20</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>150</v>
+      </c>
       <c r="F5" s="46"/>
       <c r="G5" s="46"/>
       <c r="H5" s="46" t="s">

--- a/templates/check_android_ai.xlsx
+++ b/templates/check_android_ai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutoReport_AI\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB9606C-276E-4585-9785-EBFDC14FDC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B18DCED-D8DE-405C-8358-8C2F1C9DB202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="155">
   <si>
     <t>分類</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>測項</t>
-  </si>
-  <si>
-    <t>判定結果</t>
   </si>
   <si>
     <t>備註</t>
@@ -470,38 +467,306 @@
   </si>
   <si>
     <t>更新日期：2026/0X/0X</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Report</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Fuzzing Test</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>請填入資料(如果是low或以上，先寫反例，在寫正例)</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>於測試範圍內未發現可進一步影響、繞過或削弱其他已驗證安全機制之明確證據，亦未發現因逆向結果而直接影響其他資安測試項目判定結果之情形，本項缺失目前所造成之直接安全影響有限。</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>目前情況</t>
   </si>
   <si>
     <t>Report_ch</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>cvss</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>score</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試方式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試結果：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>既有防護／限制條件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>修補建議</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>判定結果</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試方式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>透過</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>grypr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>進行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sbom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>檢測。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試結果：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>無發現</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>風險，但是會建議廠商持續根據第三方套件的最新版，進行持續更版。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊條件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">
+- 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>既有防護／限制條件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -590,12 +855,21 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
-1.</t>
+</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -605,7 +879,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -615,7 +889,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -625,7 +899,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -635,7 +909,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -645,7 +919,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -654,7 +928,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -664,7 +938,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -674,7 +948,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -684,7 +958,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -694,7 +968,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -704,7 +978,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -713,7 +987,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -723,7 +997,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -732,7 +1006,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -742,7 +1016,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -772,7 +1046,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -782,7 +1056,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -791,7 +1065,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -801,7 +1075,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
@@ -810,7 +1084,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -820,7 +1094,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
@@ -829,7 +1103,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -839,7 +1113,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
@@ -848,7 +1122,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -905,7 +1179,7 @@
       </rPr>
       <t>。</t>
     </r>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -931,7 +1205,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="細明體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -941,7 +1215,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -950,7 +1224,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
         <charset val="136"/>
@@ -990,7 +1264,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -999,7 +1273,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
         <charset val="136"/>
@@ -1016,127 +1290,7 @@
       </rPr>
       <t>。</t>
     </r>
-    <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>測試方式：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>透過</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>grypr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>進行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>sbom</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>檢測。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>測試結果：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>無發現</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>風險，但是會建議廠商持續根據第三方套件的最新版，進行持續更版。</t>
-    </r>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1229,67 +1383,47 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
-        <charset val="136"/>
       </rPr>
-      <t>無</t>
+      <t>發現</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>發現高風險。有</t>
+      <t>XX</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
-      <t>10</t>
+      <t>個高風險，</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>個中風險，但是因為真實使用情境不會發生，故判定可以降低風險，有</t>
+      <t>XX</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
-      <t>個低風險，但是判斷風險值極低</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>。</t>
+      <t>個中風險。</t>
     </r>
     <r>
       <rPr>
@@ -1324,7 +1458,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
@@ -1333,7 +1467,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -1373,7 +1507,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
@@ -1382,21 +1516,21 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
       </rPr>
       <t>。</t>
     </r>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34">
+  <fonts count="39">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1446,21 +1580,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="3"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="2"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -1506,12 +1625,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1618,6 +1731,60 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="2"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1857,62 +2024,58 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1922,28 +2085,28 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1953,47 +2116,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2391,2416 +2556,2411 @@
     <col min="4" max="4" width="25.53515625" customWidth="1"/>
     <col min="5" max="5" width="49.15234375" style="3" customWidth="1"/>
     <col min="6" max="6" width="41.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="24.3828125" customWidth="1"/>
-    <col min="8" max="8" width="54.23046875" customWidth="1"/>
-    <col min="9" max="9" width="21.3046875" customWidth="1"/>
-    <col min="10" max="10" width="38.23046875" customWidth="1"/>
+    <col min="7" max="7" width="54.23046875" customWidth="1"/>
+    <col min="8" max="8" width="21.3046875" customWidth="1"/>
+    <col min="9" max="9" width="38.23046875" customWidth="1"/>
+    <col min="11" max="11" width="28.921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.149999999999999">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11" s="56" customFormat="1" ht="20.149999999999999">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="I1" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="K1" s="55" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="150" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="B2" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="3" spans="1:11" ht="150" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+    </row>
+    <row r="4" spans="1:11" ht="150" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="1:11" ht="150" customHeight="1">
+      <c r="A5" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="150" customHeight="1">
-      <c r="A2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-    </row>
-    <row r="3" spans="1:11" ht="150" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-    </row>
-    <row r="4" spans="1:11" ht="150" customHeight="1">
-      <c r="A4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-    </row>
-    <row r="5" spans="1:11" ht="150" customHeight="1">
-      <c r="A5" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:11" ht="25" customHeight="1">
-      <c r="A6" s="24"/>
+      <c r="A6" s="22"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="45"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+    </row>
+    <row r="7" spans="1:11" ht="120" customHeight="1">
+      <c r="A7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-    </row>
-    <row r="7" spans="1:11" ht="25" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>51</v>
-      </c>
       <c r="B7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="47" t="str">
+        <v>39</v>
+      </c>
+      <c r="C7" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-STORAGE\MASTG-TEST-0001.md","Testing Local Storage for Sensitive Data")</f>
         <v>Testing Local Storage for Sensitive Data</v>
       </c>
-      <c r="D7" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-    </row>
-    <row r="8" spans="1:11" ht="25" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="D7" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+    </row>
+    <row r="8" spans="1:11" ht="120" customHeight="1">
+      <c r="A8" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="47" t="str">
+      <c r="C8" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-STORAGE\MASTG-TEST-0003.md","Testing Logs for Sensitive Data")</f>
         <v>Testing Logs for Sensitive Data</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-    </row>
-    <row r="9" spans="1:11" ht="25" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>51</v>
+      <c r="D8" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+    </row>
+    <row r="9" spans="1:11" ht="120" customHeight="1">
+      <c r="A9" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="47" t="str">
+        <v>40</v>
+      </c>
+      <c r="C9" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-STORAGE\MASTG-TEST-0004.md","Determining Whether Sensitive Data Is Shared with Third Parties via Embedded Services")</f>
         <v>Determining Whether Sensitive Data Is Shared with Third Parties via Embedded Services</v>
       </c>
-      <c r="D9" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-    </row>
-    <row r="10" spans="1:11" ht="25" customHeight="1">
-      <c r="A10" s="20" t="s">
-        <v>51</v>
+      <c r="D9" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+    </row>
+    <row r="10" spans="1:11" ht="120" customHeight="1">
+      <c r="A10" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="47" t="str">
+        <v>52</v>
+      </c>
+      <c r="C10" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-STORAGE\MASTG-TEST-0005.md","Determining Whether Sensitive Data Is Shared with Third Parties via Notifications")</f>
         <v>Determining Whether Sensitive Data Is Shared with Third Parties via Notifications</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-    </row>
-    <row r="11" spans="1:11" ht="25" customHeight="1">
-      <c r="A11" s="20" t="s">
-        <v>51</v>
+      <c r="D10" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+    </row>
+    <row r="11" spans="1:11" ht="120" customHeight="1">
+      <c r="A11" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="47" t="str">
+        <v>41</v>
+      </c>
+      <c r="C11" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-STORAGE\MASTG-TEST-0006.md","Determining Whether the Keyboard Cache Is Disabled for Text Input Fields")</f>
         <v>Determining Whether the Keyboard Cache Is Disabled for Text Input Fields</v>
       </c>
-      <c r="D11" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-    </row>
-    <row r="12" spans="1:11" ht="25" customHeight="1">
-      <c r="A12" s="20" t="s">
-        <v>51</v>
+      <c r="D11" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+    </row>
+    <row r="12" spans="1:11" ht="120" customHeight="1">
+      <c r="A12" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="47" t="str">
+        <v>42</v>
+      </c>
+      <c r="C12" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-STORAGE\MASTG-TEST-0009.md","Testing Backups for Sensitive Data")</f>
         <v>Testing Backups for Sensitive Data</v>
       </c>
-      <c r="D12" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-    </row>
-    <row r="13" spans="1:11" ht="25" customHeight="1">
-      <c r="A13" s="20" t="s">
-        <v>51</v>
+      <c r="D12" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+    </row>
+    <row r="13" spans="1:11" ht="120" customHeight="1">
+      <c r="A13" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="47" t="str">
+        <v>43</v>
+      </c>
+      <c r="C13" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-STORAGE\MASTG-TEST-0011.md","Testing Memory for Sensitive Data")</f>
         <v>Testing Memory for Sensitive Data</v>
       </c>
-      <c r="D13" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-    </row>
-    <row r="14" spans="1:11" ht="25" customHeight="1">
-      <c r="A14" s="20" t="s">
-        <v>51</v>
+      <c r="D13" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+    </row>
+    <row r="14" spans="1:11" ht="120" customHeight="1">
+      <c r="A14" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="47" t="str">
+        <v>44</v>
+      </c>
+      <c r="C14" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-STORAGE\MASTG-TEST-0012.md","Testing the Device-Access-Security Policy")</f>
         <v>Testing the Device-Access-Security Policy</v>
       </c>
-      <c r="D14" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
+      <c r="D14" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A15" s="20" t="s">
-        <v>51</v>
+      <c r="A15" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="47" t="str">
+        <v>53</v>
+      </c>
+      <c r="C15" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-STORAGE\MASTG-TEST-0052.md","Testing Local Data Storage")</f>
         <v>Testing Local Data Storage</v>
       </c>
-      <c r="D15" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46">
+      <c r="D15" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53">
         <v>1</v>
       </c>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A16" s="20" t="s">
-        <v>51</v>
+      <c r="A16" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="47" t="str">
+        <v>54</v>
+      </c>
+      <c r="C16" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-STORAGE\MASTG-TEST-0053.md","Checking Logs for Sensitive Data")</f>
         <v>Checking Logs for Sensitive Data</v>
       </c>
-      <c r="D16" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46">
+      <c r="D16" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53">
         <v>1</v>
       </c>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-    </row>
-    <row r="17" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A17" s="20" t="s">
-        <v>51</v>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+    </row>
+    <row r="17" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A17" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="47" t="str">
+        <v>55</v>
+      </c>
+      <c r="C17" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-STORAGE\MASTG-TEST-0054.md","Determining Whether Sensitive Data Is Shared with Third Parties")</f>
         <v>Determining Whether Sensitive Data Is Shared with Third Parties</v>
       </c>
-      <c r="D17" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46">
+      <c r="D17" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53">
         <v>1</v>
       </c>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-    </row>
-    <row r="18" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A18" s="20" t="s">
-        <v>51</v>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+    </row>
+    <row r="18" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A18" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="47" t="str">
+        <v>56</v>
+      </c>
+      <c r="C18" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-STORAGE\MASTG-TEST-0055.md","Finding Sensitive Data in the Keyboard Cache")</f>
         <v>Finding Sensitive Data in the Keyboard Cache</v>
       </c>
-      <c r="D18" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46">
+      <c r="D18" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53">
         <v>1</v>
       </c>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-    </row>
-    <row r="19" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A19" s="20" t="s">
-        <v>51</v>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+    </row>
+    <row r="19" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A19" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="47" t="str">
+        <v>57</v>
+      </c>
+      <c r="C19" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-STORAGE\MASTG-TEST-0058.md","Testing Backups for Sensitive Data")</f>
         <v>Testing Backups for Sensitive Data</v>
       </c>
-      <c r="D19" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46">
+      <c r="D19" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53">
         <v>1</v>
       </c>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-    </row>
-    <row r="20" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A20" s="20" t="s">
-        <v>51</v>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+    </row>
+    <row r="20" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A20" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="47" t="str">
+        <v>58</v>
+      </c>
+      <c r="C20" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-STORAGE\MASTG-TEST-0060.md","Testing Memory for Sensitive Data")</f>
         <v>Testing Memory for Sensitive Data</v>
       </c>
-      <c r="D20" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46">
+      <c r="D20" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53">
         <v>1</v>
       </c>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-    </row>
-    <row r="21" spans="1:11" ht="25" customHeight="1">
-      <c r="A21" s="20"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="26" t="s">
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+    </row>
+    <row r="21" spans="1:10" ht="25" customHeight="1">
+      <c r="A21" s="18"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="25"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+    </row>
+    <row r="22" spans="1:10" ht="120" customHeight="1">
+      <c r="A22" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-    </row>
-    <row r="22" spans="1:11" ht="25" customHeight="1">
-      <c r="A22" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="47" t="str">
+      <c r="C22" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CRYPTO\MASTG-TEST-0013.md","Testing Symmetric Cryptography")</f>
         <v>Testing Symmetric Cryptography</v>
       </c>
-      <c r="D22" s="48" t="s">
+      <c r="D22" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-    </row>
-    <row r="23" spans="1:11" ht="25" customHeight="1">
-      <c r="A23" s="20" t="s">
-        <v>51</v>
+      <c r="E22" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+    </row>
+    <row r="23" spans="1:10" ht="120" customHeight="1">
+      <c r="A23" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="47" t="str">
+        <v>61</v>
+      </c>
+      <c r="C23" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CRYPTO\MASTG-TEST-0014.md","Testing the Configuration of Cryptographic Standard Algorithms")</f>
         <v>Testing the Configuration of Cryptographic Standard Algorithms</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-    </row>
-    <row r="24" spans="1:11" ht="25" customHeight="1">
-      <c r="A24" s="20" t="s">
-        <v>51</v>
+      <c r="E23" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+    </row>
+    <row r="24" spans="1:10" ht="120" customHeight="1">
+      <c r="A24" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="47" t="str">
+        <v>62</v>
+      </c>
+      <c r="C24" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CRYPTO\MASTG-TEST-0015.md","Testing the Purposes of Keys")</f>
         <v>Testing the Purposes of Keys</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-    </row>
-    <row r="25" spans="1:11" ht="25" customHeight="1">
-      <c r="A25" s="20" t="s">
-        <v>51</v>
+      <c r="E24" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+    </row>
+    <row r="25" spans="1:10" ht="120" customHeight="1">
+      <c r="A25" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="47" t="str">
+        <v>63</v>
+      </c>
+      <c r="C25" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CRYPTO\MASTG-TEST-0016.md","Testing Random Number Generation")</f>
         <v>Testing Random Number Generation</v>
       </c>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-    </row>
-    <row r="26" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A26" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="47" t="str">
+      <c r="E25" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+    </row>
+    <row r="26" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A26" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-CRYPTO\MASTG-TEST-0061.md","Verifying the Configuration of Cryptographic Standard Algorithms")</f>
         <v>Verifying the Configuration of Cryptographic Standard Algorithms</v>
       </c>
-      <c r="D26" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46">
+      <c r="D26" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53">
         <v>1</v>
       </c>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-    </row>
-    <row r="27" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>51</v>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+    </row>
+    <row r="27" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A27" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="47" t="str">
+        <v>65</v>
+      </c>
+      <c r="C27" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-CRYPTO\MASTG-TEST-0062.md","Testing Key Management")</f>
         <v>Testing Key Management</v>
       </c>
-      <c r="D27" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46">
+      <c r="D27" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53">
         <v>1</v>
       </c>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-    </row>
-    <row r="28" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A28" s="20" t="s">
-        <v>51</v>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+    </row>
+    <row r="28" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A28" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="47" t="str">
+        <v>66</v>
+      </c>
+      <c r="C28" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-CRYPTO\MASTG-TEST-0063.md","Testing Random Number Generation")</f>
         <v>Testing Random Number Generation</v>
       </c>
-      <c r="D28" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46">
+      <c r="D28" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53">
         <v>1</v>
       </c>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-    </row>
-    <row r="29" spans="1:11" ht="25" customHeight="1">
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+    </row>
+    <row r="29" spans="1:10" ht="25" customHeight="1">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+    </row>
+    <row r="30" spans="1:10" ht="120" customHeight="1">
+      <c r="A30" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="48"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-    </row>
-    <row r="30" spans="1:11" ht="25" customHeight="1">
-      <c r="A30" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="47" t="str">
+      <c r="C30" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-AUTH\MASTG-TEST-0017.md","Testing Confirm Credentials")</f>
         <v>Testing Confirm Credentials</v>
       </c>
-      <c r="D30" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-    </row>
-    <row r="31" spans="1:11" ht="25" customHeight="1">
-      <c r="A31" s="20" t="s">
-        <v>51</v>
+      <c r="D30" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+    </row>
+    <row r="31" spans="1:10" ht="120" customHeight="1">
+      <c r="A31" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="47" t="str">
+        <v>69</v>
+      </c>
+      <c r="C31" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-AUTH\MASTG-TEST-0018.md","Testing Biometric Authentication")</f>
         <v>Testing Biometric Authentication</v>
       </c>
-      <c r="D31" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-    </row>
-    <row r="32" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A32" s="20" t="s">
-        <v>51</v>
+      <c r="D31" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+    </row>
+    <row r="32" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A32" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="47" t="str">
+        <v>70</v>
+      </c>
+      <c r="C32" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-AUTH\MASTG-TEST-0064.md","Testing Biometric Authentication")</f>
         <v>Testing Biometric Authentication</v>
       </c>
-      <c r="D32" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46">
+      <c r="D32" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53">
         <v>1</v>
       </c>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-    </row>
-    <row r="33" spans="1:11" ht="25" customHeight="1">
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+    </row>
+    <row r="33" spans="1:10" ht="25" customHeight="1">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="48"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-    </row>
-    <row r="34" spans="1:11" ht="25" customHeight="1">
-      <c r="A34" s="20" t="s">
-        <v>51</v>
+      <c r="C33" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="45"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+    </row>
+    <row r="34" spans="1:10" ht="120" customHeight="1">
+      <c r="A34" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="47" t="str">
+        <v>45</v>
+      </c>
+      <c r="C34" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-NETWORK\MASTG-TEST-0019.md","Testing Data Encryption on the Network")</f>
         <v>Testing Data Encryption on the Network</v>
       </c>
-      <c r="D34" s="48" t="s">
+      <c r="D34" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-    </row>
-    <row r="35" spans="1:11" ht="25" customHeight="1">
-      <c r="A35" s="20" t="s">
-        <v>51</v>
+      <c r="E34" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+    </row>
+    <row r="35" spans="1:10" ht="120" customHeight="1">
+      <c r="A35" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="47" t="str">
+        <v>72</v>
+      </c>
+      <c r="C35" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-NETWORK\MASTG-TEST-0020.md","Testing the TLS Settings")</f>
         <v>Testing the TLS Settings</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-    </row>
-    <row r="36" spans="1:11" ht="25" customHeight="1">
-      <c r="A36" s="20" t="s">
-        <v>51</v>
+      <c r="E35" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+    </row>
+    <row r="36" spans="1:10" ht="120" customHeight="1">
+      <c r="A36" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="47" t="str">
+        <v>73</v>
+      </c>
+      <c r="C36" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-NETWORK\MASTG-TEST-0021.md","Testing Endpoint Identify Verification")</f>
         <v>Testing Endpoint Identify Verification</v>
       </c>
-      <c r="D36" s="48" t="s">
+      <c r="D36" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-    </row>
-    <row r="37" spans="1:11" ht="25" customHeight="1">
-      <c r="A37" s="20" t="s">
-        <v>51</v>
+      <c r="E36" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+    </row>
+    <row r="37" spans="1:10" ht="120" customHeight="1">
+      <c r="A37" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="47" t="str">
+        <v>74</v>
+      </c>
+      <c r="C37" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-NETWORK\MASTG-TEST-0022.md","Testing Custom Certificate Stores and Certificate Pinning")</f>
         <v>Testing Custom Certificate Stores and Certificate Pinning</v>
       </c>
-      <c r="D37" s="48" t="s">
+      <c r="D37" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-    </row>
-    <row r="38" spans="1:11" ht="25" customHeight="1">
-      <c r="A38" s="20" t="s">
-        <v>51</v>
+      <c r="E37" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+    </row>
+    <row r="38" spans="1:10" ht="120" customHeight="1">
+      <c r="A38" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="47" t="str">
+        <v>75</v>
+      </c>
+      <c r="C38" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-NETWORK\MASTG-TEST-0023.md","Testing the Security Provider")</f>
         <v>Testing the Security Provider</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-    </row>
-    <row r="39" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A39" s="20" t="s">
-        <v>51</v>
+      <c r="E38" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+    </row>
+    <row r="39" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A39" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="47" t="str">
+        <v>76</v>
+      </c>
+      <c r="C39" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-NETWORK\MASTG-TEST-0065.md","Testing Data Encryption on the Network")</f>
         <v>Testing Data Encryption on the Network</v>
       </c>
-      <c r="D39" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="46">
+      <c r="D39" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53">
         <v>1</v>
       </c>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-    </row>
-    <row r="40" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A40" s="20" t="s">
-        <v>51</v>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+    </row>
+    <row r="40" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A40" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="47" t="str">
+        <v>77</v>
+      </c>
+      <c r="C40" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-NETWORK\MASTG-TEST-0066.md","Testing the TLS Settings")</f>
         <v>Testing the TLS Settings</v>
       </c>
-      <c r="D40" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="46">
+      <c r="D40" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53">
         <v>1</v>
       </c>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
-    </row>
-    <row r="41" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A41" s="20" t="s">
-        <v>51</v>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+    </row>
+    <row r="41" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A41" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" s="47" t="str">
+        <v>78</v>
+      </c>
+      <c r="C41" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-NETWORK\MASTG-TEST-0067.md","Testing Endpoint Identity Verification")</f>
         <v>Testing Endpoint Identity Verification</v>
       </c>
-      <c r="D41" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="46"/>
-      <c r="H41" s="46">
+      <c r="D41" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53">
         <v>1</v>
       </c>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
-      <c r="K41" s="46"/>
-    </row>
-    <row r="42" spans="1:11" ht="25" hidden="1" customHeight="1">
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+    </row>
+    <row r="42" spans="1:10" ht="25" hidden="1" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="47" t="str">
+        <v>79</v>
+      </c>
+      <c r="C42" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-NETWORK\MASTG-TEST-0068.md","Testing Custom Certificate Stores and Certificate Pinning")</f>
         <v>Testing Custom Certificate Stores and Certificate Pinning</v>
       </c>
-      <c r="D42" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="46">
+      <c r="D42" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53">
         <v>1</v>
       </c>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
-    </row>
-    <row r="43" spans="1:11" ht="25" customHeight="1">
-      <c r="A43" s="20"/>
+      <c r="H42" s="53"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+    </row>
+    <row r="43" spans="1:10" ht="25" customHeight="1">
+      <c r="A43" s="18"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" s="48"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-    </row>
-    <row r="44" spans="1:11" ht="25" customHeight="1">
-      <c r="A44" s="20" t="s">
-        <v>51</v>
+      <c r="C43" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="45"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+    </row>
+    <row r="44" spans="1:10" ht="120" customHeight="1">
+      <c r="A44" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="47" t="str">
+        <v>46</v>
+      </c>
+      <c r="C44" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0007.md","Determining Whether Sensitive Stored Data Has Been Exposed via IPC Mechanisms")</f>
         <v>Determining Whether Sensitive Stored Data Has Been Exposed via IPC Mechanisms</v>
       </c>
-      <c r="D44" s="48" t="s">
+      <c r="D44" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-    </row>
-    <row r="45" spans="1:11" ht="25" customHeight="1">
-      <c r="A45" s="20" t="s">
-        <v>51</v>
+      <c r="E44" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+    </row>
+    <row r="45" spans="1:10" ht="120" customHeight="1">
+      <c r="A45" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="47" t="str">
+        <v>81</v>
+      </c>
+      <c r="C45" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0008.md","Checking for Sensitive Data Disclosure Through the User Interface")</f>
         <v>Checking for Sensitive Data Disclosure Through the User Interface</v>
       </c>
-      <c r="D45" s="48" t="s">
+      <c r="D45" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-    </row>
-    <row r="46" spans="1:11" ht="25" customHeight="1">
-      <c r="A46" s="20" t="s">
-        <v>51</v>
+      <c r="E45" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+    </row>
+    <row r="46" spans="1:10" ht="120" customHeight="1">
+      <c r="A46" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C46" s="47" t="str">
+        <v>82</v>
+      </c>
+      <c r="C46" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0010.md","Finding Sensitive Information in Auto-Generated Screenshots")</f>
         <v>Finding Sensitive Information in Auto-Generated Screenshots</v>
       </c>
-      <c r="D46" s="48" t="s">
+      <c r="D46" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="46"/>
-    </row>
-    <row r="47" spans="1:11" ht="25" customHeight="1">
-      <c r="A47" s="20" t="s">
-        <v>51</v>
+      <c r="E46" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+    </row>
+    <row r="47" spans="1:10" ht="120" customHeight="1">
+      <c r="A47" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="47" t="str">
+        <v>83</v>
+      </c>
+      <c r="C47" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0024.md","Testing for App Permissions")</f>
         <v>Testing for App Permissions</v>
       </c>
-      <c r="D47" s="48" t="s">
+      <c r="D47" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-    </row>
-    <row r="48" spans="1:11" ht="25" customHeight="1">
-      <c r="A48" s="20" t="s">
-        <v>51</v>
+      <c r="E47" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+    </row>
+    <row r="48" spans="1:10" ht="120" customHeight="1">
+      <c r="A48" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" s="47" t="str">
+        <v>84</v>
+      </c>
+      <c r="C48" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0028.md","Testing Deep Links")</f>
         <v>Testing Deep Links</v>
       </c>
-      <c r="D48" s="48" t="s">
+      <c r="D48" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="46"/>
-    </row>
-    <row r="49" spans="1:11" ht="25" customHeight="1">
-      <c r="A49" s="20" t="s">
-        <v>51</v>
+      <c r="E48" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+    </row>
+    <row r="49" spans="1:10" ht="120" customHeight="1">
+      <c r="A49" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" s="47" t="str">
+        <v>85</v>
+      </c>
+      <c r="C49" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0029.md","Testing for Sensitive Functionality Exposure Through IPC")</f>
         <v>Testing for Sensitive Functionality Exposure Through IPC</v>
       </c>
-      <c r="D49" s="48" t="s">
+      <c r="D49" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-    </row>
-    <row r="50" spans="1:11" ht="25" customHeight="1">
-      <c r="A50" s="20" t="s">
-        <v>51</v>
+      <c r="E49" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+    </row>
+    <row r="50" spans="1:10" ht="120" customHeight="1">
+      <c r="A50" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" s="47" t="str">
+        <v>86</v>
+      </c>
+      <c r="C50" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0030.md","Testing for Vulnerable Implementation of PendingIntent")</f>
         <v>Testing for Vulnerable Implementation of PendingIntent</v>
       </c>
-      <c r="D50" s="48" t="s">
+      <c r="D50" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-    </row>
-    <row r="51" spans="1:11" ht="25" customHeight="1">
-      <c r="A51" s="20" t="s">
-        <v>51</v>
+      <c r="E50" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+    </row>
+    <row r="51" spans="1:10" ht="120" customHeight="1">
+      <c r="A51" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="47" t="str">
+        <v>87</v>
+      </c>
+      <c r="C51" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0031.md","Testing JavaScript Execution in WebViews")</f>
         <v>Testing JavaScript Execution in WebViews</v>
       </c>
-      <c r="D51" s="48" t="s">
+      <c r="D51" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-    </row>
-    <row r="52" spans="1:11" ht="25" customHeight="1">
-      <c r="A52" s="20" t="s">
-        <v>51</v>
+      <c r="E51" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+    </row>
+    <row r="52" spans="1:10" ht="120" customHeight="1">
+      <c r="A52" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" s="47" t="str">
+        <v>88</v>
+      </c>
+      <c r="C52" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0032.md","Testing WebView Protocol Handlers")</f>
         <v>Testing WebView Protocol Handlers</v>
       </c>
-      <c r="D52" s="48" t="s">
+      <c r="D52" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-    </row>
-    <row r="53" spans="1:11" ht="25" customHeight="1">
-      <c r="A53" s="20" t="s">
-        <v>51</v>
+      <c r="E52" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+    </row>
+    <row r="53" spans="1:10" ht="120" customHeight="1">
+      <c r="A53" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" s="47" t="str">
+        <v>89</v>
+      </c>
+      <c r="C53" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0033.md","Testing for Java Objects Exposed Through WebViews")</f>
         <v>Testing for Java Objects Exposed Through WebViews</v>
       </c>
-      <c r="D53" s="48" t="s">
+      <c r="D53" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
-      <c r="K53" s="46"/>
-    </row>
-    <row r="54" spans="1:11" ht="25" customHeight="1">
-      <c r="A54" s="20" t="s">
-        <v>51</v>
+      <c r="E53" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+    </row>
+    <row r="54" spans="1:10" ht="120" customHeight="1">
+      <c r="A54" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="47" t="str">
+        <v>90</v>
+      </c>
+      <c r="C54" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0035.md","Testing for Overlay Attacks")</f>
         <v>Testing for Overlay Attacks</v>
       </c>
-      <c r="D54" s="48" t="s">
+      <c r="D54" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-    </row>
-    <row r="55" spans="1:11" ht="25" customHeight="1">
-      <c r="A55" s="20" t="s">
-        <v>51</v>
+      <c r="E54" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+    </row>
+    <row r="55" spans="1:10" ht="120" customHeight="1">
+      <c r="A55" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="47" t="str">
+        <v>91</v>
+      </c>
+      <c r="C55" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-PLATFORM\MASTG-TEST-0037.md","Testing WebViews Cleanup")</f>
         <v>Testing WebViews Cleanup</v>
       </c>
-      <c r="D55" s="48" t="s">
+      <c r="D55" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-    </row>
-    <row r="56" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A56" s="20" t="s">
-        <v>51</v>
+      <c r="E55" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+    </row>
+    <row r="56" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A56" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" s="47" t="str">
+        <v>92</v>
+      </c>
+      <c r="C56" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0056.md","Determining Whether Sensitive Data Is Exposed via IPC Mechanisms")</f>
         <v>Determining Whether Sensitive Data Is Exposed via IPC Mechanisms</v>
       </c>
-      <c r="D56" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46">
+      <c r="D56" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53">
         <v>1</v>
       </c>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-    </row>
-    <row r="57" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A57" s="20" t="s">
-        <v>51</v>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+    </row>
+    <row r="57" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A57" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C57" s="47" t="str">
+        <v>93</v>
+      </c>
+      <c r="C57" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0057.md","Checking for Sensitive Data Disclosed Through the User Interface")</f>
         <v>Checking for Sensitive Data Disclosed Through the User Interface</v>
       </c>
-      <c r="D57" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="46">
+      <c r="D57" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="53"/>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53">
         <v>1</v>
       </c>
-      <c r="I57" s="46"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="46"/>
-    </row>
-    <row r="58" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A58" s="20" t="s">
-        <v>51</v>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+    </row>
+    <row r="58" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A58" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" s="47" t="str">
+        <v>94</v>
+      </c>
+      <c r="C58" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0059.md","Testing Auto-Generated Screenshots for Sensitive Information")</f>
         <v>Testing Auto-Generated Screenshots for Sensitive Information</v>
       </c>
-      <c r="D58" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46">
+      <c r="D58" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53">
         <v>1</v>
       </c>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
-    </row>
-    <row r="59" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A59" s="20" t="s">
-        <v>51</v>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+    </row>
+    <row r="59" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A59" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" s="47" t="str">
+        <v>95</v>
+      </c>
+      <c r="C59" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0069.md","Testing App Permissions")</f>
         <v>Testing App Permissions</v>
       </c>
-      <c r="D59" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46">
+      <c r="D59" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53">
         <v>1</v>
       </c>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
-    </row>
-    <row r="60" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A60" s="20" t="s">
-        <v>51</v>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="53"/>
+    </row>
+    <row r="60" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A60" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" s="47" t="str">
+        <v>96</v>
+      </c>
+      <c r="C60" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0070.md","Testing Universal Links")</f>
         <v>Testing Universal Links</v>
       </c>
-      <c r="D60" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46">
+      <c r="D60" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53">
         <v>1</v>
       </c>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-    </row>
-    <row r="61" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A61" s="20" t="s">
-        <v>51</v>
+      <c r="H60" s="53"/>
+      <c r="I60" s="53"/>
+      <c r="J60" s="53"/>
+    </row>
+    <row r="61" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A61" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C61" s="47" t="str">
+        <v>97</v>
+      </c>
+      <c r="C61" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0071.md","Testing UIActivity Sharing")</f>
         <v>Testing UIActivity Sharing</v>
       </c>
-      <c r="D61" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46">
+      <c r="D61" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="53"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53">
         <v>1</v>
       </c>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46"/>
-      <c r="K61" s="46"/>
-    </row>
-    <row r="62" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A62" s="20" t="s">
-        <v>51</v>
+      <c r="H61" s="53"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="53"/>
+    </row>
+    <row r="62" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A62" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C62" s="47" t="str">
+        <v>98</v>
+      </c>
+      <c r="C62" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0072.md","Testing App Extensions")</f>
         <v>Testing App Extensions</v>
       </c>
-      <c r="D62" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" s="46"/>
-      <c r="F62" s="46"/>
-      <c r="G62" s="46"/>
-      <c r="H62" s="46">
+      <c r="D62" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53">
         <v>1</v>
       </c>
-      <c r="I62" s="46"/>
-      <c r="J62" s="46"/>
-      <c r="K62" s="46"/>
-    </row>
-    <row r="63" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A63" s="20" t="s">
-        <v>51</v>
+      <c r="H62" s="53"/>
+      <c r="I62" s="53"/>
+      <c r="J62" s="53"/>
+    </row>
+    <row r="63" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A63" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C63" s="47" t="str">
+        <v>99</v>
+      </c>
+      <c r="C63" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0073.md","Testing UIPasteboard")</f>
         <v>Testing UIPasteboard</v>
       </c>
-      <c r="D63" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46">
+      <c r="D63" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="53"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53">
         <v>1</v>
       </c>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="46"/>
-    </row>
-    <row r="64" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A64" s="20" t="s">
-        <v>51</v>
+      <c r="H63" s="53"/>
+      <c r="I63" s="53"/>
+      <c r="J63" s="53"/>
+    </row>
+    <row r="64" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A64" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C64" s="47" t="str">
+        <v>100</v>
+      </c>
+      <c r="C64" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0075.md","Testing Custom URL Schemes")</f>
         <v>Testing Custom URL Schemes</v>
       </c>
-      <c r="D64" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="46">
+      <c r="D64" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53">
         <v>1</v>
       </c>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-    </row>
-    <row r="65" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A65" s="20" t="s">
-        <v>51</v>
+      <c r="H64" s="53"/>
+      <c r="I64" s="53"/>
+      <c r="J64" s="53"/>
+    </row>
+    <row r="65" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A65" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C65" s="47" t="str">
+        <v>101</v>
+      </c>
+      <c r="C65" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0076.md","Testing iOS WebViews")</f>
         <v>Testing iOS WebViews</v>
       </c>
-      <c r="D65" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46">
+      <c r="D65" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53">
         <v>1</v>
       </c>
-      <c r="I65" s="46"/>
-      <c r="J65" s="46"/>
-      <c r="K65" s="46"/>
-    </row>
-    <row r="66" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A66" s="20" t="s">
-        <v>51</v>
+      <c r="H65" s="53"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+    </row>
+    <row r="66" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A66" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C66" s="47" t="str">
+        <v>102</v>
+      </c>
+      <c r="C66" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0077.md","Testing WebView Protocol Handlers")</f>
         <v>Testing WebView Protocol Handlers</v>
       </c>
-      <c r="D66" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46">
+      <c r="D66" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53">
         <v>1</v>
       </c>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
-    </row>
-    <row r="67" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A67" s="20" t="s">
-        <v>51</v>
+      <c r="H66" s="53"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+    </row>
+    <row r="67" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A67" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" s="47" t="str">
+        <v>103</v>
+      </c>
+      <c r="C67" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-PLATFORM\MASTG-TEST-0078.md","Determining Whether Native Methods Are Exposed Through WebViews")</f>
         <v>Determining Whether Native Methods Are Exposed Through WebViews</v>
       </c>
-      <c r="D67" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46">
+      <c r="D67" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53">
         <v>1</v>
       </c>
-      <c r="I67" s="46"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
-    </row>
-    <row r="68" spans="1:11" ht="25" customHeight="1">
+      <c r="H67" s="53"/>
+      <c r="I67" s="53"/>
+      <c r="J67" s="53"/>
+    </row>
+    <row r="68" spans="1:10" ht="25" customHeight="1">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
-      <c r="C68" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D68" s="48"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I68" s="46"/>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
-    </row>
-    <row r="69" spans="1:11" ht="25" customHeight="1">
-      <c r="A69" s="20" t="s">
-        <v>51</v>
+      <c r="C68" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D68" s="45"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
+      <c r="H68" s="53"/>
+      <c r="I68" s="53"/>
+      <c r="J68" s="53"/>
+    </row>
+    <row r="69" spans="1:10" ht="120" customHeight="1">
+      <c r="A69" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C69" s="47" t="str">
+        <v>47</v>
+      </c>
+      <c r="C69" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0002.md","Testing Local Storage for Input Validation")</f>
         <v>Testing Local Storage for Input Validation</v>
       </c>
-      <c r="D69" s="48" t="s">
+      <c r="D69" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I69" s="46"/>
-      <c r="J69" s="46"/>
-      <c r="K69" s="46"/>
-    </row>
-    <row r="70" spans="1:11" ht="25" customHeight="1">
-      <c r="A70" s="20" t="s">
-        <v>51</v>
+      <c r="E69" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H69" s="53"/>
+      <c r="I69" s="53"/>
+      <c r="J69" s="53"/>
+    </row>
+    <row r="70" spans="1:10" ht="120" customHeight="1">
+      <c r="A70" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C70" s="47" t="str">
+        <v>105</v>
+      </c>
+      <c r="C70" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0025.md","Testing for Injection Flaws")</f>
         <v>Testing for Injection Flaws</v>
       </c>
-      <c r="D70" s="48" t="s">
+      <c r="D70" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
-    </row>
-    <row r="71" spans="1:11" ht="25" customHeight="1">
-      <c r="A71" s="20" t="s">
-        <v>51</v>
+      <c r="E70" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H70" s="53"/>
+      <c r="I70" s="53"/>
+      <c r="J70" s="53"/>
+    </row>
+    <row r="71" spans="1:10" ht="120" customHeight="1">
+      <c r="A71" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C71" s="47" t="str">
+        <v>48</v>
+      </c>
+      <c r="C71" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0026.md","Testing Implicit Intents")</f>
         <v>Testing Implicit Intents</v>
       </c>
-      <c r="D71" s="48" t="s">
+      <c r="D71" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I71" s="46"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
-    </row>
-    <row r="72" spans="1:11" ht="25" customHeight="1">
-      <c r="A72" s="20" t="s">
-        <v>51</v>
+      <c r="E71" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H71" s="53"/>
+      <c r="I71" s="53"/>
+      <c r="J71" s="53"/>
+    </row>
+    <row r="72" spans="1:10" ht="120" customHeight="1">
+      <c r="A72" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C72" s="47" t="str">
+        <v>106</v>
+      </c>
+      <c r="C72" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0027.md","Testing for URL Loading in WebViews")</f>
         <v>Testing for URL Loading in WebViews</v>
       </c>
-      <c r="D72" s="48" t="s">
+      <c r="D72" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
-    </row>
-    <row r="73" spans="1:11" ht="25" customHeight="1">
-      <c r="A73" s="20" t="s">
-        <v>51</v>
+      <c r="E72" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F72" s="53"/>
+      <c r="G72" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H72" s="53"/>
+      <c r="I72" s="53"/>
+      <c r="J72" s="53"/>
+    </row>
+    <row r="73" spans="1:10" ht="120" customHeight="1">
+      <c r="A73" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C73" s="47" t="str">
+        <v>107</v>
+      </c>
+      <c r="C73" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0034.md","Testing Object Persistence")</f>
         <v>Testing Object Persistence</v>
       </c>
-      <c r="D73" s="48" t="s">
+      <c r="D73" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="46"/>
-      <c r="H73" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I73" s="46"/>
-      <c r="J73" s="46"/>
-      <c r="K73" s="46"/>
-    </row>
-    <row r="74" spans="1:11" ht="25" customHeight="1">
-      <c r="A74" s="20" t="s">
-        <v>51</v>
+      <c r="E73" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H73" s="53"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+    </row>
+    <row r="74" spans="1:10" ht="120" customHeight="1">
+      <c r="A74" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C74" s="47" t="str">
+        <v>108</v>
+      </c>
+      <c r="C74" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0036.md","Testing Enforced Updating")</f>
         <v>Testing Enforced Updating</v>
       </c>
-      <c r="D74" s="48" t="s">
+      <c r="D74" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I74" s="46"/>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
-    </row>
-    <row r="75" spans="1:11" ht="25" customHeight="1">
-      <c r="A75" s="20" t="s">
-        <v>51</v>
+      <c r="E74" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+    </row>
+    <row r="75" spans="1:10" ht="120" customHeight="1">
+      <c r="A75" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C75" s="47" t="str">
+        <v>109</v>
+      </c>
+      <c r="C75" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0042.md","Checking for Weaknesses in Third Party Libraries")</f>
         <v>Checking for Weaknesses in Third Party Libraries</v>
       </c>
-      <c r="D75" s="48" t="s">
+      <c r="D75" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-    </row>
-    <row r="76" spans="1:11" ht="25" customHeight="1">
-      <c r="A76" s="20" t="s">
-        <v>51</v>
+      <c r="E75" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
+      <c r="J75" s="53"/>
+    </row>
+    <row r="76" spans="1:10" ht="120" customHeight="1">
+      <c r="A76" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C76" s="47" t="str">
+        <v>110</v>
+      </c>
+      <c r="C76" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0043.md","Memory Corruption Bugs")</f>
         <v>Memory Corruption Bugs</v>
       </c>
-      <c r="D76" s="48" t="s">
+      <c r="D76" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I76" s="46"/>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
-    </row>
-    <row r="77" spans="1:11" ht="25" customHeight="1">
-      <c r="A77" s="20" t="s">
-        <v>51</v>
+      <c r="E76" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+    </row>
+    <row r="77" spans="1:10" ht="120" customHeight="1">
+      <c r="A77" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C77" s="47" t="str">
+        <v>111</v>
+      </c>
+      <c r="C77" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-CODE\MASTG-TEST-0044.md","Make Sure That Free Security Features Are Activated")</f>
         <v>Make Sure That Free Security Features Are Activated</v>
       </c>
-      <c r="D77" s="48" t="s">
+      <c r="D77" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E77" s="46"/>
-      <c r="F77" s="46"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I77" s="46"/>
-      <c r="J77" s="46"/>
-      <c r="K77" s="46"/>
-    </row>
-    <row r="78" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A78" s="20" t="s">
-        <v>51</v>
+      <c r="E77" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H77" s="53"/>
+      <c r="I77" s="53"/>
+      <c r="J77" s="53"/>
+    </row>
+    <row r="78" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A78" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C78" s="47" t="str">
+        <v>112</v>
+      </c>
+      <c r="C78" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-CODE\MASTG-TEST-0079.md","Testing Object Persistence")</f>
         <v>Testing Object Persistence</v>
       </c>
-      <c r="D78" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E78" s="46"/>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46">
+      <c r="D78" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53">
         <v>1</v>
       </c>
-      <c r="I78" s="46"/>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
-    </row>
-    <row r="79" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A79" s="20" t="s">
-        <v>51</v>
+      <c r="H78" s="53"/>
+      <c r="I78" s="53"/>
+      <c r="J78" s="53"/>
+    </row>
+    <row r="79" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A79" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C79" s="47" t="str">
+        <v>113</v>
+      </c>
+      <c r="C79" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-CODE\MASTG-TEST-0080.md","Testing Enforced Updating")</f>
         <v>Testing Enforced Updating</v>
       </c>
-      <c r="D79" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E79" s="46"/>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="46">
+      <c r="D79" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53">
         <v>1</v>
       </c>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-    </row>
-    <row r="80" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A80" s="20" t="s">
-        <v>51</v>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
+      <c r="J79" s="53"/>
+    </row>
+    <row r="80" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A80" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C80" s="47" t="str">
+        <v>114</v>
+      </c>
+      <c r="C80" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-CODE\MASTG-TEST-0085.md","Checking for Weaknesses in Third Party Libraries")</f>
         <v>Checking for Weaknesses in Third Party Libraries</v>
       </c>
-      <c r="D80" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" s="46"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
-    </row>
-    <row r="81" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A81" s="20" t="s">
-        <v>51</v>
+      <c r="D80" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
+      <c r="J80" s="53"/>
+    </row>
+    <row r="81" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A81" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C81" s="47" t="str">
+        <v>115</v>
+      </c>
+      <c r="C81" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-CODE\MASTG-TEST-0086.md","Memory Corruption Bugs")</f>
         <v>Memory Corruption Bugs</v>
       </c>
-      <c r="D81" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E81" s="46"/>
-      <c r="F81" s="46"/>
-      <c r="G81" s="46"/>
-      <c r="H81" s="46"/>
-      <c r="I81" s="46"/>
-      <c r="J81" s="46"/>
-      <c r="K81" s="46"/>
-    </row>
-    <row r="82" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A82" s="20" t="s">
-        <v>51</v>
+      <c r="D81" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" s="53"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
+      <c r="H81" s="53"/>
+      <c r="I81" s="53"/>
+      <c r="J81" s="53"/>
+    </row>
+    <row r="82" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A82" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C82" s="47" t="str">
+        <v>116</v>
+      </c>
+      <c r="C82" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-CODE\MASTG-TEST-0087.md","Make Sure That Free Security Features Are Activated")</f>
         <v>Make Sure That Free Security Features Are Activated</v>
       </c>
-      <c r="D82" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E82" s="46"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="46"/>
-    </row>
-    <row r="83" spans="1:11" ht="25" customHeight="1">
+      <c r="D82" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="53"/>
+      <c r="I82" s="53"/>
+      <c r="J82" s="53"/>
+    </row>
+    <row r="83" spans="1:10" ht="25" customHeight="1">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
-      <c r="C83" s="26" t="s">
+      <c r="C83" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D83" s="45"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53"/>
+      <c r="H83" s="53"/>
+      <c r="I83" s="53"/>
+      <c r="J83" s="53"/>
+    </row>
+    <row r="84" spans="1:10" ht="120" customHeight="1">
+      <c r="A84" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B84" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D83" s="48"/>
-      <c r="E83" s="46"/>
-      <c r="F83" s="46"/>
-      <c r="G83" s="46"/>
-      <c r="H83" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I83" s="46"/>
-      <c r="J83" s="46"/>
-      <c r="K83" s="46"/>
-    </row>
-    <row r="84" spans="1:11" ht="25" customHeight="1">
-      <c r="A84" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C84" s="47" t="str">
+      <c r="C84" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0038.md","Making Sure that the App is Properly Signed")</f>
         <v>Making Sure that the App is Properly Signed</v>
       </c>
-      <c r="D84" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E84" s="46"/>
-      <c r="F84" s="46"/>
-      <c r="G84" s="46"/>
-      <c r="H84" s="46" t="s">
+      <c r="D84" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H84" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I84" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J84" s="46"/>
-      <c r="K84" s="46"/>
-    </row>
-    <row r="85" spans="1:11" ht="25" customHeight="1">
-      <c r="A85" s="20" t="s">
-        <v>51</v>
+      <c r="I84" s="53"/>
+      <c r="J84" s="53"/>
+    </row>
+    <row r="85" spans="1:10" ht="120" customHeight="1">
+      <c r="A85" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C85" s="47" t="str">
+        <v>119</v>
+      </c>
+      <c r="C85" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0039.md","Testing whether the App is Debuggable")</f>
         <v>Testing whether the App is Debuggable</v>
       </c>
-      <c r="D85" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="46"/>
-      <c r="F85" s="46"/>
-      <c r="G85" s="46"/>
-      <c r="H85" s="46" t="s">
+      <c r="D85" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H85" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I85" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J85" s="46"/>
-      <c r="K85" s="46"/>
-    </row>
-    <row r="86" spans="1:11" ht="25" customHeight="1">
-      <c r="A86" s="20" t="s">
-        <v>51</v>
+      <c r="I85" s="53"/>
+      <c r="J85" s="53"/>
+    </row>
+    <row r="86" spans="1:10" ht="120" customHeight="1">
+      <c r="A86" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C86" s="47" t="str">
+        <v>120</v>
+      </c>
+      <c r="C86" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0040.md","Testing for Debugging Symbols")</f>
         <v>Testing for Debugging Symbols</v>
       </c>
-      <c r="D86" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="46"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46" t="s">
+      <c r="D86" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H86" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I86" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J86" s="46"/>
-      <c r="K86" s="46"/>
-    </row>
-    <row r="87" spans="1:11" ht="25" customHeight="1">
-      <c r="A87" s="20" t="s">
-        <v>51</v>
+      <c r="I86" s="53"/>
+      <c r="J86" s="53"/>
+    </row>
+    <row r="87" spans="1:10" ht="120" customHeight="1">
+      <c r="A87" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C87" s="47" t="str">
+        <v>121</v>
+      </c>
+      <c r="C87" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0041.md","Testing for Debugging Code and Verbose Error Logging")</f>
         <v>Testing for Debugging Code and Verbose Error Logging</v>
       </c>
-      <c r="D87" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46" t="s">
+      <c r="D87" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H87" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I87" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J87" s="46"/>
-      <c r="K87" s="46"/>
-    </row>
-    <row r="88" spans="1:11" ht="25" customHeight="1">
-      <c r="A88" s="20" t="s">
-        <v>51</v>
+      <c r="I87" s="53"/>
+      <c r="J87" s="53"/>
+    </row>
+    <row r="88" spans="1:10" ht="120" customHeight="1">
+      <c r="A88" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C88" s="47" t="str">
+        <v>122</v>
+      </c>
+      <c r="C88" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0045.md","Testing Root Detection")</f>
         <v>Testing Root Detection</v>
       </c>
-      <c r="D88" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="46"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46" t="s">
+      <c r="D88" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H88" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I88" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J88" s="46"/>
-      <c r="K88" s="46"/>
-    </row>
-    <row r="89" spans="1:11" ht="25" customHeight="1">
-      <c r="A89" s="20" t="s">
-        <v>51</v>
+      <c r="I88" s="53"/>
+      <c r="J88" s="53"/>
+    </row>
+    <row r="89" spans="1:10" ht="120" customHeight="1">
+      <c r="A89" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C89" s="47" t="str">
+        <v>123</v>
+      </c>
+      <c r="C89" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0046.md","Testing Anti-Debugging Detection")</f>
         <v>Testing Anti-Debugging Detection</v>
       </c>
-      <c r="D89" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E89" s="46"/>
-      <c r="F89" s="46"/>
-      <c r="G89" s="46"/>
-      <c r="H89" s="46" t="s">
+      <c r="D89" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H89" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I89" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J89" s="46"/>
-      <c r="K89" s="46"/>
-    </row>
-    <row r="90" spans="1:11" ht="25" customHeight="1">
-      <c r="A90" s="20" t="s">
-        <v>51</v>
+      <c r="I89" s="53"/>
+      <c r="J89" s="53"/>
+    </row>
+    <row r="90" spans="1:10" ht="120" customHeight="1">
+      <c r="A90" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C90" s="47" t="str">
+        <v>124</v>
+      </c>
+      <c r="C90" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0047.md","Testing File Integrity Checks")</f>
         <v>Testing File Integrity Checks</v>
       </c>
-      <c r="D90" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="46"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46" t="s">
+      <c r="D90" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H90" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I90" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J90" s="46"/>
-      <c r="K90" s="46"/>
-    </row>
-    <row r="91" spans="1:11" ht="25" customHeight="1">
-      <c r="A91" s="20" t="s">
-        <v>51</v>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+    </row>
+    <row r="91" spans="1:10" ht="120" customHeight="1">
+      <c r="A91" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C91" s="47" t="str">
+        <v>125</v>
+      </c>
+      <c r="C91" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0048.md","Testing Reverse Engineering Tools Detection")</f>
         <v>Testing Reverse Engineering Tools Detection</v>
       </c>
-      <c r="D91" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" s="46"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46" t="s">
+      <c r="D91" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F91" s="53"/>
+      <c r="G91" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H91" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I91" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J91" s="46"/>
-      <c r="K91" s="46"/>
-    </row>
-    <row r="92" spans="1:11" ht="25" customHeight="1">
-      <c r="A92" s="20" t="s">
-        <v>51</v>
+      <c r="I91" s="53"/>
+      <c r="J91" s="53"/>
+    </row>
+    <row r="92" spans="1:10" ht="120" customHeight="1">
+      <c r="A92" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C92" s="47" t="str">
+        <v>126</v>
+      </c>
+      <c r="C92" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0049.md","Testing Emulator Detection")</f>
         <v>Testing Emulator Detection</v>
       </c>
-      <c r="D92" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="46"/>
-      <c r="F92" s="46"/>
-      <c r="G92" s="46"/>
-      <c r="H92" s="46" t="s">
+      <c r="D92" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F92" s="53"/>
+      <c r="G92" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H92" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I92" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J92" s="46"/>
-      <c r="K92" s="46"/>
-    </row>
-    <row r="93" spans="1:11" ht="25" customHeight="1">
-      <c r="A93" s="20" t="s">
-        <v>51</v>
+      <c r="I92" s="53"/>
+      <c r="J92" s="53"/>
+    </row>
+    <row r="93" spans="1:10" ht="120" customHeight="1">
+      <c r="A93" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C93" s="47" t="str">
+        <v>127</v>
+      </c>
+      <c r="C93" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0050.md","Testing Runtime Integrity Checks")</f>
         <v>Testing Runtime Integrity Checks</v>
       </c>
-      <c r="D93" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" s="46"/>
-      <c r="F93" s="46"/>
-      <c r="G93" s="46"/>
-      <c r="H93" s="46" t="s">
+      <c r="D93" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F93" s="53"/>
+      <c r="G93" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H93" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I93" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J93" s="46"/>
-      <c r="K93" s="46"/>
-    </row>
-    <row r="94" spans="1:11" ht="25" customHeight="1">
-      <c r="A94" s="20" t="s">
-        <v>51</v>
+      <c r="I93" s="53"/>
+      <c r="J93" s="53"/>
+    </row>
+    <row r="94" spans="1:10" ht="120" customHeight="1">
+      <c r="A94" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C94" s="47" t="str">
+        <v>128</v>
+      </c>
+      <c r="C94" s="44" t="str">
         <f>HYPERLINK(".\tests\android\MASVS-RESILIENCE\MASTG-TEST-0051.md","Testing Obfuscation")</f>
         <v>Testing Obfuscation</v>
       </c>
-      <c r="D94" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="46"/>
-      <c r="F94" s="46"/>
-      <c r="G94" s="46"/>
-      <c r="H94" s="46" t="s">
+      <c r="D94" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="H94" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="I94" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J94" s="46"/>
-      <c r="K94" s="46"/>
-    </row>
-    <row r="95" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A95" s="20" t="s">
-        <v>51</v>
+      <c r="I94" s="53"/>
+      <c r="J94" s="53"/>
+    </row>
+    <row r="95" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A95" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C95" s="47" t="str">
+        <v>129</v>
+      </c>
+      <c r="C95" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0081.md","Making Sure that the App Is Properly Signed")</f>
         <v>Making Sure that the App Is Properly Signed</v>
       </c>
-      <c r="D95" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E95" s="27"/>
+      <c r="D95" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="25"/>
       <c r="F95" s="5"/>
     </row>
-    <row r="96" spans="1:11" ht="25" hidden="1" customHeight="1">
-      <c r="A96" s="20" t="s">
-        <v>51</v>
+    <row r="96" spans="1:10" ht="25" hidden="1" customHeight="1">
+      <c r="A96" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C96" s="47" t="str">
+        <v>130</v>
+      </c>
+      <c r="C96" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0082.md","Testing whether the App is Debuggable")</f>
         <v>Testing whether the App is Debuggable</v>
       </c>
-      <c r="D96" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E96" s="27"/>
+      <c r="D96" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="25"/>
       <c r="F96" s="5"/>
     </row>
     <row r="97" spans="1:6" ht="25" hidden="1" customHeight="1">
-      <c r="A97" s="20" t="s">
-        <v>51</v>
+      <c r="A97" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C97" s="47" t="str">
+        <v>131</v>
+      </c>
+      <c r="C97" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0083.md","Testing for Debugging Symbols")</f>
         <v>Testing for Debugging Symbols</v>
       </c>
-      <c r="D97" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E97" s="27"/>
+      <c r="D97" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="25"/>
       <c r="F97" s="5"/>
     </row>
     <row r="98" spans="1:6" ht="25" hidden="1" customHeight="1">
-      <c r="A98" s="20" t="s">
-        <v>51</v>
+      <c r="A98" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C98" s="47" t="str">
+        <v>132</v>
+      </c>
+      <c r="C98" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0084.md","Testing for Debugging Code and Verbose Error Logging")</f>
         <v>Testing for Debugging Code and Verbose Error Logging</v>
       </c>
-      <c r="D98" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E98" s="27"/>
+      <c r="D98" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" s="25"/>
       <c r="F98" s="5"/>
     </row>
     <row r="99" spans="1:6" ht="25" hidden="1" customHeight="1">
-      <c r="A99" s="20" t="s">
-        <v>51</v>
+      <c r="A99" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C99" s="47" t="str">
+        <v>133</v>
+      </c>
+      <c r="C99" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0088.md","Testing Jailbreak Detection")</f>
         <v>Testing Jailbreak Detection</v>
       </c>
-      <c r="D99" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E99" s="27"/>
+      <c r="D99" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="25"/>
       <c r="F99" s="5"/>
     </row>
     <row r="100" spans="1:6" ht="25" hidden="1" customHeight="1">
-      <c r="A100" s="20" t="s">
-        <v>51</v>
+      <c r="A100" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C100" s="47" t="str">
+        <v>134</v>
+      </c>
+      <c r="C100" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0089.md","Testing Anti-Debugging Detection")</f>
         <v>Testing Anti-Debugging Detection</v>
       </c>
-      <c r="D100" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" s="27"/>
+      <c r="D100" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" s="25"/>
       <c r="F100" s="5"/>
     </row>
     <row r="101" spans="1:6" ht="25" hidden="1" customHeight="1">
-      <c r="A101" s="20" t="s">
-        <v>51</v>
+      <c r="A101" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C101" s="47" t="str">
+        <v>135</v>
+      </c>
+      <c r="C101" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0090.md","Testing File Integrity Checks")</f>
         <v>Testing File Integrity Checks</v>
       </c>
-      <c r="D101" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" s="27"/>
+      <c r="D101" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="25"/>
       <c r="F101" s="5"/>
     </row>
     <row r="102" spans="1:6" ht="25" hidden="1" customHeight="1">
-      <c r="A102" s="20" t="s">
-        <v>51</v>
+      <c r="A102" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C102" s="47" t="str">
+        <v>136</v>
+      </c>
+      <c r="C102" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0091.md","Testing Reverse Engineering Tools Detection")</f>
         <v>Testing Reverse Engineering Tools Detection</v>
       </c>
-      <c r="D102" s="48" t="s">
-        <v>20</v>
+      <c r="D102" s="45" t="s">
+        <v>19</v>
       </c>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
     </row>
     <row r="103" spans="1:6" ht="25" hidden="1" customHeight="1">
-      <c r="A103" s="20" t="s">
-        <v>51</v>
+      <c r="A103" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C103" s="47" t="str">
+        <v>137</v>
+      </c>
+      <c r="C103" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0092.md","Testing Emulator Detection")</f>
         <v>Testing Emulator Detection</v>
       </c>
-      <c r="D103" s="48" t="s">
-        <v>20</v>
+      <c r="D103" s="45" t="s">
+        <v>19</v>
       </c>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
     </row>
     <row r="104" spans="1:6" ht="25" hidden="1" customHeight="1">
-      <c r="A104" s="20" t="s">
-        <v>51</v>
+      <c r="A104" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C104" s="47" t="str">
+        <v>138</v>
+      </c>
+      <c r="C104" s="44" t="str">
         <f>HYPERLINK(".\tests\ios\MASVS-RESILIENCE\MASTG-TEST-0093.md","Testing Obfuscation")</f>
         <v>Testing Obfuscation</v>
       </c>
-      <c r="D104" s="48" t="s">
-        <v>20</v>
+      <c r="D104" s="45" t="s">
+        <v>19</v>
       </c>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
@@ -4825,8 +4985,8 @@
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
-      <c r="D107" s="18" t="s">
-        <v>16</v>
+      <c r="D107" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
@@ -4835,8 +4995,8 @@
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
-      <c r="D108" s="11" t="s">
-        <v>17</v>
+      <c r="D108" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
@@ -4845,8 +5005,8 @@
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
-      <c r="D109" s="17" t="s">
-        <v>18</v>
+      <c r="D109" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -4855,8 +5015,8 @@
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
-      <c r="D110" s="10" t="s">
-        <v>19</v>
+      <c r="D110" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
@@ -4865,8 +5025,8 @@
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
-      <c r="D111" s="14" t="s">
-        <v>20</v>
+      <c r="D111" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
@@ -4875,8 +5035,8 @@
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
-      <c r="D112" s="15" t="s">
-        <v>21</v>
+      <c r="D112" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
@@ -4885,8 +5045,8 @@
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
-      <c r="D113" s="19" t="s">
-        <v>22</v>
+      <c r="D113" s="17" t="s">
+        <v>21</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
@@ -4895,8 +5055,8 @@
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
-      <c r="D114" s="19" t="s">
-        <v>23</v>
+      <c r="D114" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
@@ -12085,7 +12245,7 @@
       </customFilters>
     </filterColumn>
   </autoFilter>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="D2:D20 D22:D104">
     <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"Not Applicable"</formula>
@@ -12126,62 +12286,62 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="15.45"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="9.84375" style="30" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="30" customWidth="1"/>
-    <col min="4" max="4" width="34.07421875" style="31" customWidth="1"/>
-    <col min="5" max="5" width="76.3828125" style="30" customWidth="1"/>
-    <col min="6" max="6" width="68.3046875" style="31" customWidth="1"/>
-    <col min="7" max="16384" width="9.15234375" style="30"/>
+    <col min="1" max="1" width="27.69140625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="9.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="28" customWidth="1"/>
+    <col min="4" max="4" width="34.07421875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="76.3828125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="68.3046875" style="29" customWidth="1"/>
+    <col min="7" max="16384" width="9.15234375" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="77.150000000000006">
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="27" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="29" t="s">
+      <c r="B3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="C3" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="D3" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>4</v>
+      <c r="F3" s="30" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="35"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="45"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="43"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="35"/>
-      <c r="C5" s="44"/>
+      <c r="A5" s="33"/>
+      <c r="C5" s="42"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="35"/>
-      <c r="C6" s="44"/>
+      <c r="A6" s="33"/>
+      <c r="C6" s="42"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="35"/>
-      <c r="C7" s="44"/>
+      <c r="A7" s="33"/>
+      <c r="C7" s="42"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="C4:C7">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"Not Applicable"</formula>
@@ -12234,7 +12394,7 @@
     <col min="1" max="1" width="9.23046875" customWidth="1"/>
     <col min="2" max="2" width="9.84375" customWidth="1"/>
     <col min="3" max="4" width="32.15234375" customWidth="1"/>
-    <col min="5" max="5" width="15.84375" style="39" customWidth="1"/>
+    <col min="5" max="5" width="15.84375" style="37" customWidth="1"/>
     <col min="6" max="6" width="14.84375" customWidth="1"/>
     <col min="7" max="7" width="21.15234375" customWidth="1"/>
     <col min="8" max="8" width="13.69140625" customWidth="1"/>
@@ -12245,170 +12405,170 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="12.45" customHeight="1">
-      <c r="D1" s="42"/>
-    </row>
-    <row r="2" spans="1:18" s="40" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="51" t="s">
+      <c r="D1" s="40"/>
+    </row>
+    <row r="2" spans="1:18" s="38" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="39"/>
+      <c r="B2" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="D2" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="F2" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="G2" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="52" t="s">
+      <c r="H2" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="I2" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="J2" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="52" t="s">
+      <c r="K2" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="55"/>
+      <c r="L2" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="52"/>
     </row>
     <row r="3" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
     </row>
     <row r="5" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A5" s="37"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
     </row>
     <row r="6" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
       <c r="E6"/>
-      <c r="G6" s="28"/>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
       <c r="E7"/>
-      <c r="G7" s="28"/>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="35"/>
       <c r="E8"/>
     </row>
     <row r="9" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
       <c r="E9"/>
     </row>
     <row r="10" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="35"/>
       <c r="E10"/>
     </row>
     <row r="11" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="35"/>
       <c r="E11"/>
       <c r="R11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
       <c r="E12"/>
     </row>
     <row r="13" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
       <c r="E13"/>
     </row>
     <row r="14" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
       <c r="E14"/>
     </row>
     <row r="15" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
       <c r="E15"/>
     </row>
     <row r="16" spans="1:18" ht="12.55" customHeight="1">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
       <c r="E16"/>
     </row>
     <row r="17" spans="1:5" ht="12.55" customHeight="1">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
       <c r="E17"/>
     </row>
     <row r="18" spans="1:5" ht="12.55" customHeight="1">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
       <c r="E18"/>
     </row>
     <row r="19" spans="1:5" ht="12.55" customHeight="1">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
       <c r="E19"/>
     </row>
     <row r="20" spans="1:5" ht="12.55" customHeight="1">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
       <c r="E20"/>
     </row>
     <row r="21" spans="1:5" ht="12.55" customHeight="1">
-      <c r="A21" s="37"/>
-      <c r="B21" s="37"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
       <c r="E21"/>
     </row>
     <row r="22" spans="1:5" ht="12.55" customHeight="1">
@@ -12421,12 +12581,12 @@
       <c r="E24"/>
     </row>
     <row r="25" spans="1:5" ht="12.55" customHeight="1">
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
     </row>
     <row r="26" spans="1:5" ht="12.55" customHeight="1">
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
     </row>
     <row r="27" spans="1:5" ht="12.55" customHeight="1"/>
     <row r="28" spans="1:5" ht="12.55" customHeight="1"/>
@@ -12436,7 +12596,7 @@
     <row r="32" spans="1:5" ht="12.55" customHeight="1"/>
     <row r="33" ht="12.55" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12450,50 +12610,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="14.15">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="14.15">
+      <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="14.15">
-      <c r="A2" s="11" t="s">
+    <row r="3" spans="1:1" ht="14.15">
+      <c r="A3" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="14.15">
-      <c r="A3" s="17" t="s">
+    <row r="4" spans="1:1" ht="14.15">
+      <c r="A4" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14.15">
-      <c r="A4" s="10" t="s">
+    <row r="5" spans="1:1" ht="14.15">
+      <c r="A5" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="14.15">
-      <c r="A5" s="14" t="s">
+    <row r="6" spans="1:1" ht="14.15">
+      <c r="A6" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="14.15">
-      <c r="A6" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="7" spans="1:1" ht="14.15">
-      <c r="A7" s="19" t="s">
-        <v>39</v>
+      <c r="A7" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="14.15">
-      <c r="A8" s="19" t="s">
-        <v>23</v>
+      <c r="A8" s="17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="14.15">
-      <c r="A9" s="36"/>
+      <c r="A9" s="34"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12503,7 +12663,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.45"/>
   <sheetData/>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
